--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>92.40799713134766</v>
+        <v>89.00299835205078</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>92.40799713134766</v>
+        <v>89.00299835205078</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>92.40799713134766</v>
+        <v>89.00299835205078</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>92.40799713134766</v>
+        <v>89.00299835205078</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>92.30038452148438</v>
+        <v>92.09035491943359</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>92.30038452148438</v>
+        <v>92.09035491943359</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>92.30038452148438</v>
+        <v>92.09035491943359</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>92.30038452148438</v>
+        <v>92.09035491943359</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>93.60023498535156</v>
+        <v>91.98310089111328</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>93.60023498535156</v>
+        <v>91.98310089111328</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>93.60023498535156</v>
+        <v>91.98310089111328</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>93.60023498535156</v>
+        <v>91.98310089111328</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>93.36566925048828</v>
+        <v>93.27849578857422</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>93.36566925048828</v>
+        <v>93.27849578857422</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>93.36566925048828</v>
+        <v>93.27849578857422</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>93.36566925048828</v>
+        <v>93.27849578857422</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>93.3834228515625</v>
+        <v>93.04473114013672</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>93.3834228515625</v>
+        <v>93.04473114013672</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>93.3834228515625</v>
+        <v>93.04473114013672</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>93.3834228515625</v>
+        <v>93.04473114013672</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>93.52400970458984</v>
+        <v>93.06243133544922</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>93.52400970458984</v>
+        <v>93.06243133544922</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>93.52400970458984</v>
+        <v>93.06243133544922</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>93.52400970458984</v>
+        <v>93.06243133544922</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>95.74551391601562</v>
+        <v>93.20253753662109</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>95.74551391601562</v>
+        <v>93.20253753662109</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>95.74551391601562</v>
+        <v>93.20253753662109</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>95.74551391601562</v>
+        <v>93.20253753662109</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>93.4376220703125</v>
+        <v>95.41637420654297</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>93.4376220703125</v>
+        <v>95.41637420654297</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>93.4376220703125</v>
+        <v>95.41637420654297</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>93.4376220703125</v>
+        <v>95.41637420654297</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>93.65187072753906</v>
+        <v>93.11642456054688</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>93.65187072753906</v>
+        <v>93.11642456054688</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>93.65187072753906</v>
+        <v>93.11642456054688</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>93.65187072753906</v>
+        <v>93.11642456054688</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>94.37021636962891</v>
+        <v>93.32994842529297</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>94.37021636962891</v>
+        <v>93.32994842529297</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>94.37021636962891</v>
+        <v>93.32994842529297</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>94.37021636962891</v>
+        <v>93.32994842529297</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>93.44683074951172</v>
+        <v>94.04581451416016</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>93.44683074951172</v>
+        <v>94.04581451416016</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>93.44683074951172</v>
+        <v>94.04581451416016</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>93.44683074951172</v>
+        <v>94.04581451416016</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.78685760498047</v>
+        <v>93.1256103515625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.78685760498047</v>
+        <v>93.1256103515625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.78685760498047</v>
+        <v>93.1256103515625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.78685760498047</v>
+        <v>93.1256103515625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>92.18663787841797</v>
+        <v>92.46791839599609</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>92.18663787841797</v>
+        <v>92.46791839599609</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>92.18663787841797</v>
+        <v>92.46791839599609</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>92.18663787841797</v>
+        <v>92.46791839599609</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>81.64599609375</v>
+        <v>80.95899963378906</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>81.64599609375</v>
+        <v>80.95899963378906</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>81.64599609375</v>
+        <v>80.95899963378906</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>81.64599609375</v>
+        <v>80.95899963378906</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.50541687011719</v>
+        <v>81.40367889404297</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>81.50541687011719</v>
+        <v>81.40367889404297</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>81.50541687011719</v>
+        <v>81.40367889404297</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>81.50541687011719</v>
+        <v>81.40367889404297</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>81.37818908691406</v>
+        <v>81.26351165771484</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>81.37818908691406</v>
+        <v>81.26351165771484</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>81.37818908691406</v>
+        <v>81.26351165771484</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>81.37818908691406</v>
+        <v>81.26351165771484</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>81.32566070556641</v>
+        <v>81.13666534423828</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>81.32566070556641</v>
+        <v>81.13666534423828</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>81.32566070556641</v>
+        <v>81.13666534423828</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>81.32566070556641</v>
+        <v>81.13666534423828</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.26341247558594</v>
+        <v>81.08428955078125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.26341247558594</v>
+        <v>81.08428955078125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.26341247558594</v>
+        <v>81.08428955078125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.26341247558594</v>
+        <v>81.08428955078125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.10871887207031</v>
+        <v>81.022216796875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.10871887207031</v>
+        <v>81.022216796875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.10871887207031</v>
+        <v>81.022216796875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.10871887207031</v>
+        <v>81.022216796875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.48887634277344</v>
+        <v>80.86798858642578</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.48887634277344</v>
+        <v>80.86798858642578</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.48887634277344</v>
+        <v>80.86798858642578</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.48887634277344</v>
+        <v>80.86798858642578</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.05780792236328</v>
+        <v>81.24700164794922</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.05780792236328</v>
+        <v>81.24700164794922</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.05780792236328</v>
+        <v>81.24700164794922</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.05780792236328</v>
+        <v>81.24700164794922</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.89176177978516</v>
+        <v>80.81723785400391</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.89176177978516</v>
+        <v>80.81723785400391</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.89176177978516</v>
+        <v>80.81723785400391</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.89176177978516</v>
+        <v>80.81723785400391</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.65404510498047</v>
+        <v>80.65167999267578</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.65404510498047</v>
+        <v>80.65167999267578</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.65404510498047</v>
+        <v>80.65167999267578</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.65404510498047</v>
+        <v>80.65167999267578</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.30165100097656</v>
+        <v>80.41466522216797</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.30165100097656</v>
+        <v>80.41466522216797</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.30165100097656</v>
+        <v>80.41466522216797</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.30165100097656</v>
+        <v>80.41466522216797</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>80.03455352783203</v>
+        <v>80.06333160400391</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>80.03455352783203</v>
+        <v>80.06333160400391</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>80.03455352783203</v>
+        <v>80.06333160400391</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>80.03455352783203</v>
+        <v>80.06333160400391</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.80495452880859</v>
+        <v>79.79702758789062</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.80495452880859</v>
+        <v>79.79702758789062</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.80495452880859</v>
+        <v>79.79702758789062</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.80495452880859</v>
+        <v>79.79702758789062</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>716.760009765625</v>
+        <v>739.77001953125</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>716.760009765625</v>
+        <v>739.77001953125</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>716.760009765625</v>
+        <v>739.77001953125</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>716.760009765625</v>
+        <v>739.77001953125</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.013916015625</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.013916015625</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.013916015625</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.013916015625</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.2738647460938</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.2738647460938</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.2738647460938</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.2738647460938</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>735.6334838867188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>735.6334838867188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>735.6334838867188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>735.6334838867188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>736.7318115234375</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>736.7318115234375</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>736.7318115234375</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>736.7318115234375</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>666.3126831054688</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>666.3126831054688</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>666.3126831054688</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>666.3126831054688</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>605.859375</v>
+        <v>575.9462280273438</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>605.859375</v>
+        <v>575.9462280273438</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>605.859375</v>
+        <v>575.9462280273438</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>605.859375</v>
+        <v>575.9462280273438</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>605.228759765625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>605.228759765625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>605.228759765625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>605.228759765625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>619.75927734375</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>619.75927734375</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>619.75927734375</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>619.75927734375</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>612.2249145507812</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>612.2249145507812</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>612.2249145507812</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>612.2249145507812</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>616.35400390625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>616.35400390625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>616.35400390625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>616.35400390625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>626.128173828125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>626.128173828125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>626.128173828125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>626.128173828125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>567.666015625</v>
+        <v>597.5623779296875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>567.666015625</v>
+        <v>597.5623779296875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>567.666015625</v>
+        <v>597.5623779296875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>567.666015625</v>
+        <v>597.5623779296875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>704.8900146484375</v>
+        <v>700.8599853515625</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>704.8900146484375</v>
+        <v>700.8599853515625</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>704.8900146484375</v>
+        <v>700.8599853515625</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>704.8900146484375</v>
+        <v>700.8599853515625</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>703.0821533203125</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>703.0821533203125</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>703.0821533203125</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>703.0821533203125</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>684.8889770507812</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>684.8889770507812</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>684.8889770507812</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>684.8889770507812</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>685.0485229492188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>685.0485229492188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>685.0485229492188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>685.0485229492188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>691.6919555664062</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>691.6919555664062</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>691.6919555664062</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>691.6919555664062</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>656.97265625</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>656.97265625</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>656.97265625</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>656.97265625</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>594.286865234375</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>594.286865234375</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>594.286865234375</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>594.286865234375</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>625.619140625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>625.619140625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>625.619140625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>625.619140625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>630.7545776367188</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>630.7545776367188</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>630.7545776367188</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>630.7545776367188</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>621.7427368164062</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>621.7427368164062</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>621.7427368164062</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>621.7427368164062</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>621.2535400390625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>621.2535400390625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>621.2535400390625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>621.2535400390625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>619.8991088867188</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>619.8991088867188</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>619.8991088867188</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>619.8991088867188</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>586.1571655273438</v>
+        <v>605.4061279296875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>586.1571655273438</v>
+        <v>605.4061279296875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>586.1571655273438</v>
+        <v>605.4061279296875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>586.1571655273438</v>
+        <v>605.4061279296875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>87.31999969482422</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>87.31999969482422</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>87.31999969482422</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>87.31999969482422</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.16252136230469</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.16252136230469</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.16252136230469</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.16252136230469</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.43743896484375</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.43743896484375</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.43743896484375</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.43743896484375</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.33582305908203</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.33582305908203</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.33582305908203</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.33582305908203</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.51988983154297</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.51988983154297</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.51988983154297</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.51988983154297</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.53871917724609</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.53871917724609</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.53871917724609</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.53871917724609</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.62606048583984</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.62606048583984</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.62606048583984</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.62606048583984</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.19765472412109</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.19765472412109</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.19765472412109</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.19765472412109</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.07798767089844</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.07798767089844</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.07798767089844</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.07798767089844</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>74.88881683349609</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>74.88881683349609</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>74.88881683349609</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>74.88881683349609</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.05070495605469</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.05070495605469</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.05070495605469</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.05070495605469</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.74851226806641</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.74851226806641</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.74851226806641</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.74851226806641</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>69.35610198974609</v>
+        <v>71.60801696777344</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>69.35610198974609</v>
+        <v>71.60801696777344</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>69.35610198974609</v>
+        <v>71.60801696777344</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>69.35610198974609</v>
+        <v>71.60801696777344</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>71.98699951171875</v>
+        <v>69.9010009765625</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>71.98699951171875</v>
+        <v>69.9010009765625</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>71.98699951171875</v>
+        <v>69.9010009765625</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>71.98699951171875</v>
+        <v>69.9010009765625</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>71.72592163085938</v>
+        <v>71.73148345947266</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>71.72592163085938</v>
+        <v>71.73148345947266</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>71.72592163085938</v>
+        <v>71.73148345947266</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>71.72592163085938</v>
+        <v>71.73148345947266</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72.65538787841797</v>
+        <v>71.47133636474609</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>72.65538787841797</v>
+        <v>71.47133636474609</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>72.65538787841797</v>
+        <v>71.47133636474609</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>72.65538787841797</v>
+        <v>71.47133636474609</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>72.46041107177734</v>
+        <v>72.39749908447266</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>72.46041107177734</v>
+        <v>72.39749908447266</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>72.46041107177734</v>
+        <v>72.39749908447266</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>72.46041107177734</v>
+        <v>72.39749908447266</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>72.26116943359375</v>
+        <v>72.20321655273438</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>72.26116943359375</v>
+        <v>72.20321655273438</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>72.26116943359375</v>
+        <v>72.20321655273438</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>72.26116943359375</v>
+        <v>72.20321655273438</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>72.15300750732422</v>
+        <v>72.00467681884766</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>72.15300750732422</v>
+        <v>72.00467681884766</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>72.15300750732422</v>
+        <v>72.00467681884766</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>72.15300750732422</v>
+        <v>72.00467681884766</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.42873382568359</v>
+        <v>71.89690399169922</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.42873382568359</v>
+        <v>71.89690399169922</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.42873382568359</v>
+        <v>71.89690399169922</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.42873382568359</v>
+        <v>71.89690399169922</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.27118682861328</v>
+        <v>73.16809844970703</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.27118682861328</v>
+        <v>73.16809844970703</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.27118682861328</v>
+        <v>73.16809844970703</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.27118682861328</v>
+        <v>73.16809844970703</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.11540222167969</v>
+        <v>72.0146484375</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.11540222167969</v>
+        <v>72.0146484375</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.11540222167969</v>
+        <v>72.0146484375</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.11540222167969</v>
+        <v>72.0146484375</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>72.33251190185547</v>
+        <v>71.85942077636719</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>72.33251190185547</v>
+        <v>71.85942077636719</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>72.33251190185547</v>
+        <v>71.85942077636719</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>72.33251190185547</v>
+        <v>71.85942077636719</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.90304565429688</v>
+        <v>72.07575988769531</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.90304565429688</v>
+        <v>72.07575988769531</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.90304565429688</v>
+        <v>72.07575988769531</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.90304565429688</v>
+        <v>72.07575988769531</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.47209167480469</v>
+        <v>71.6478271484375</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.47209167480469</v>
+        <v>71.6478271484375</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.47209167480469</v>
+        <v>71.6478271484375</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.47209167480469</v>
+        <v>71.6478271484375</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>70.69078063964844</v>
+        <v>71.21840667724609</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>70.69078063964844</v>
+        <v>71.21840667724609</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.69078063964844</v>
+        <v>71.21840667724609</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>70.69078063964844</v>
+        <v>71.21840667724609</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.3800048828125</v>
+        <v>91.37699890136719</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.3800048828125</v>
+        <v>91.37699890136719</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.3800048828125</v>
+        <v>91.37699890136719</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.3800048828125</v>
+        <v>91.37699890136719</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.12777709960938</v>
+        <v>91.11775207519531</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.12777709960938</v>
+        <v>91.11775207519531</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.12777709960938</v>
+        <v>91.11775207519531</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.12777709960938</v>
+        <v>91.11775207519531</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>90.82164001464844</v>
+        <v>90.86624908447266</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>90.82164001464844</v>
+        <v>90.86624908447266</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>90.82164001464844</v>
+        <v>90.86624908447266</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>90.82164001464844</v>
+        <v>90.86624908447266</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.57485961914062</v>
+        <v>90.56098175048828</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.57485961914062</v>
+        <v>90.56098175048828</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.57485961914062</v>
+        <v>90.56098175048828</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.57485961914062</v>
+        <v>90.56098175048828</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.28828430175781</v>
+        <v>90.31491088867188</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.28828430175781</v>
+        <v>90.31491088867188</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.28828430175781</v>
+        <v>90.31491088867188</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.28828430175781</v>
+        <v>90.31491088867188</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.02818298339844</v>
+        <v>90.0291748046875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.02818298339844</v>
+        <v>90.0291748046875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.02818298339844</v>
+        <v>90.0291748046875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.02818298339844</v>
+        <v>90.0291748046875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>89.76979827880859</v>
+        <v>89.76980590820312</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>89.76979827880859</v>
+        <v>89.76980590820312</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>89.76979827880859</v>
+        <v>89.76980590820312</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>89.76979827880859</v>
+        <v>89.76980590820312</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.53074645996094</v>
+        <v>89.51217651367188</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.53074645996094</v>
+        <v>89.51217651367188</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.53074645996094</v>
+        <v>89.51217651367188</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.53074645996094</v>
+        <v>89.51217651367188</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.26698303222656</v>
+        <v>89.27378845214844</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.26698303222656</v>
+        <v>89.27378845214844</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.26698303222656</v>
+        <v>89.27378845214844</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.26698303222656</v>
+        <v>89.27378845214844</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>88.96875</v>
+        <v>89.01078033447266</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>88.96875</v>
+        <v>89.01078033447266</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>88.96875</v>
+        <v>89.01078033447266</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>88.96875</v>
+        <v>89.01078033447266</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.71364593505859</v>
+        <v>88.71342468261719</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.71364593505859</v>
+        <v>88.71342468261719</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.71364593505859</v>
+        <v>88.71342468261719</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.71364593505859</v>
+        <v>88.71342468261719</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.40330505371094</v>
+        <v>88.45904541015625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.40330505371094</v>
+        <v>88.45904541015625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.40330505371094</v>
+        <v>88.45904541015625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.40330505371094</v>
+        <v>88.45904541015625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>88.1123046875</v>
+        <v>88.14958953857422</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>88.1123046875</v>
+        <v>88.14958953857422</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>88.1123046875</v>
+        <v>88.14958953857422</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>88.1123046875</v>
+        <v>88.14958953857422</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>160.1000061035156</v>
+        <v>155.25</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>160.1000061035156</v>
+        <v>155.25</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>160.1000061035156</v>
+        <v>155.25</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>160.1000061035156</v>
+        <v>155.25</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>159.8004455566406</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>159.8004455566406</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>159.8004455566406</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>159.8004455566406</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.2383575439453</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.2383575439453</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.2383575439453</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.2383575439453</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.0012969970703</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.0012969970703</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.0012969970703</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.0012969970703</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>159.8240814208984</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>159.8240814208984</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>159.8240814208984</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>159.8240814208984</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>156.9353332519531</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>156.9353332519531</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>156.9353332519531</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>156.9353332519531</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.7251739501953</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.7251739501953</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.7251739501953</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.7251739501953</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>158.8810272216797</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>158.8810272216797</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>158.8810272216797</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>158.8810272216797</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.3861541748047</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.3861541748047</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.3861541748047</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.3861541748047</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.2831420898438</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.2831420898438</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.2831420898438</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.2831420898438</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>139.3867340087891</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>139.3867340087891</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>139.3867340087891</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>139.3867340087891</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.0293273925781</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.0293273925781</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.0293273925781</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.0293273925781</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>138.2135620117188</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>138.2135620117188</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>138.2135620117188</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>138.2135620117188</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.20499420166016</v>
+        <v>77.46799468994141</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.20499420166016</v>
+        <v>77.46799468994141</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.20499420166016</v>
+        <v>77.46799468994141</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.20499420166016</v>
+        <v>77.46799468994141</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.60728454589844</v>
+        <v>81.875244140625</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>81.60728454589844</v>
+        <v>81.875244140625</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>81.60728454589844</v>
+        <v>81.875244140625</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>81.60728454589844</v>
+        <v>81.875244140625</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85.42919158935547</v>
+        <v>81.27993011474609</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>85.42919158935547</v>
+        <v>81.27993011474609</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>85.42919158935547</v>
+        <v>81.27993011474609</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>85.42919158935547</v>
+        <v>81.27993011474609</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>84.44461059570312</v>
+        <v>85.08650207519531</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>84.44461059570312</v>
+        <v>85.08650207519531</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>84.44461059570312</v>
+        <v>85.08650207519531</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>84.44461059570312</v>
+        <v>85.08650207519531</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>83.99658966064453</v>
+        <v>84.10586547851562</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>83.99658966064453</v>
+        <v>84.10586547851562</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>83.99658966064453</v>
+        <v>84.10586547851562</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>83.99658966064453</v>
+        <v>84.10586547851562</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>84.70783996582031</v>
+        <v>83.65964508056641</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>84.70783996582031</v>
+        <v>83.65964508056641</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>84.70783996582031</v>
+        <v>83.65964508056641</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>84.70783996582031</v>
+        <v>83.65964508056641</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>88.44928741455078</v>
+        <v>84.36805725097656</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>88.44928741455078</v>
+        <v>84.36805725097656</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>88.44928741455078</v>
+        <v>84.36805725097656</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>88.44928741455078</v>
+        <v>84.36805725097656</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>84.53227996826172</v>
+        <v>88.09449768066406</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>84.53227996826172</v>
+        <v>88.09449768066406</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>84.53227996826172</v>
+        <v>88.09449768066406</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>84.53227996826172</v>
+        <v>88.09449768066406</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>84.56138610839844</v>
+        <v>84.19319915771484</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>84.56138610839844</v>
+        <v>84.19319915771484</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>84.56138610839844</v>
+        <v>84.19319915771484</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>84.56138610839844</v>
+        <v>84.19319915771484</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>86.87094116210938</v>
+        <v>84.22217559814453</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>86.87094116210938</v>
+        <v>84.22217559814453</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>86.87094116210938</v>
+        <v>84.22217559814453</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>86.87094116210938</v>
+        <v>84.22217559814453</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>86.63501739501953</v>
+        <v>86.52247619628906</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>86.63501739501953</v>
+        <v>86.52247619628906</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>86.63501739501953</v>
+        <v>86.52247619628906</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>86.63501739501953</v>
+        <v>86.52247619628906</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>85.45480346679688</v>
+        <v>86.28749084472656</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>85.45480346679688</v>
+        <v>86.28749084472656</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>85.45480346679688</v>
+        <v>86.28749084472656</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>85.45480346679688</v>
+        <v>86.28749084472656</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>82.49253082275391</v>
+        <v>85.11201477050781</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>82.49253082275391</v>
+        <v>85.11201477050781</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>82.49253082275391</v>
+        <v>85.11201477050781</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>82.49253082275391</v>
+        <v>85.11201477050781</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>60.52000045776367</v>
+        <v>59.31000137329102</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>60.52000045776367</v>
+        <v>59.31000137329102</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>60.52000045776367</v>
+        <v>59.31000137329102</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>60.52000045776367</v>
+        <v>59.31000137329102</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>58.75</v>
+        <v>60.40483856201172</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>58.75</v>
+        <v>60.40483856201172</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>58.75</v>
+        <v>60.40483856201172</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>58.75</v>
+        <v>60.40483856201172</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.63820648193359</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.63820648193359</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.63820648193359</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.63820648193359</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.576416015625</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.576416015625</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.576416015625</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.576416015625</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.69511032104492</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.69511032104492</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.69511032104492</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.69511032104492</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.74804306030273</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.74804306030273</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.74804306030273</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.74804306030273</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.88310623168945</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.88310623168945</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.88310623168945</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.88310623168945</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>57.92060089111328</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>57.92060089111328</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>57.92060089111328</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>57.92060089111328</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.29563903808594</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.29563903808594</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.29563903808594</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.29563903808594</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.5940055847168</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.5940055847168</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.5940055847168</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.5940055847168</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.08868408203125</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.08868408203125</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.08868408203125</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.08868408203125</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.74374389648438</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.74374389648438</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.74374389648438</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.74374389648438</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>52.97136688232422</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>52.97136688232422</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>52.97136688232422</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>52.97136688232422</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>105.765998840332</v>
+        <v>101.7409973144531</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>105.765998840332</v>
+        <v>101.7409973144531</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>105.765998840332</v>
+        <v>101.7409973144531</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>105.765998840332</v>
+        <v>101.7409973144531</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>105.3497467041016</v>
+        <v>105.3115921020508</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>105.3497467041016</v>
+        <v>105.3115921020508</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>105.3497467041016</v>
+        <v>105.3115921020508</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>105.3497467041016</v>
+        <v>105.3115921020508</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>107.7670974731445</v>
+        <v>104.8971252441406</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>107.7670974731445</v>
+        <v>104.8971252441406</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>107.7670974731445</v>
+        <v>104.8971252441406</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>107.7670974731445</v>
+        <v>104.8971252441406</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>107.6455688476562</v>
+        <v>107.304084777832</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>107.6455688476562</v>
+        <v>107.304084777832</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>107.6455688476562</v>
+        <v>107.304084777832</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>107.6455688476562</v>
+        <v>107.304084777832</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>106.725227355957</v>
+        <v>107.1830825805664</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>106.725227355957</v>
+        <v>107.1830825805664</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>106.725227355957</v>
+        <v>107.1830825805664</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>106.725227355957</v>
+        <v>107.1830825805664</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>106.4252090454102</v>
+        <v>106.2666931152344</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>106.4252090454102</v>
+        <v>106.2666931152344</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>106.4252090454102</v>
+        <v>106.2666931152344</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>106.4252090454102</v>
+        <v>106.2666931152344</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>108.6779098510742</v>
+        <v>105.9679641723633</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>108.6779098510742</v>
+        <v>105.9679641723633</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>108.6779098510742</v>
+        <v>105.9679641723633</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>108.6779098510742</v>
+        <v>105.9679641723633</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>107.2007141113281</v>
+        <v>108.2109909057617</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>107.2007141113281</v>
+        <v>108.2109909057617</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>107.2007141113281</v>
+        <v>108.2109909057617</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>107.2007141113281</v>
+        <v>108.2109909057617</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>106.8323135375977</v>
+        <v>106.7401504516602</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>106.8323135375977</v>
+        <v>106.7401504516602</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>106.8323135375977</v>
+        <v>106.7401504516602</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>106.8323135375977</v>
+        <v>106.7401504516602</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>107.6260070800781</v>
+        <v>106.3732986450195</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>107.6260070800781</v>
+        <v>106.3732986450195</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>107.6260070800781</v>
+        <v>106.3732986450195</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>107.6260070800781</v>
+        <v>106.3732986450195</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>106.6330718994141</v>
+        <v>107.1636123657227</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>106.6330718994141</v>
+        <v>107.1636123657227</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>106.6330718994141</v>
+        <v>107.1636123657227</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>106.6330718994141</v>
+        <v>107.1636123657227</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>106.4739379882812</v>
+        <v>106.174934387207</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>106.4739379882812</v>
+        <v>106.174934387207</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>106.4739379882812</v>
+        <v>106.174934387207</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>106.4739379882812</v>
+        <v>106.174934387207</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>104.5119934082031</v>
+        <v>106.016471862793</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>104.5119934082031</v>
+        <v>106.016471862793</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>104.5119934082031</v>
+        <v>106.016471862793</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>104.5119934082031</v>
+        <v>106.016471862793</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
